--- a/downloads/exportExelCustomerNormal.xlsx
+++ b/downloads/exportExelCustomerNormal.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>Customer Name</t>
   </si>
@@ -31,25 +31,16 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Arjun Singh</t>
-  </si>
-  <si>
-    <t>akbk6551+1140@gmail.com</t>
+    <t>Mayank Rathor</t>
+  </si>
+  <si>
+    <t>akbk6551+1139@gmail.com</t>
   </si>
   <si>
     <t>individual</t>
   </si>
   <si>
-    <t>8000000016</t>
-  </si>
-  <si>
-    <t>Mayank Rathor</t>
-  </si>
-  <si>
-    <t>akbk6551+1139@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000015</t>
+    <t>9123456790</t>
   </si>
   <si>
     <t>Anil Rathor</t>
@@ -58,67 +49,67 @@
     <t>akbk6551+1136@gmail.com</t>
   </si>
   <si>
-    <t>8000000014</t>
+    <t>9103456789</t>
   </si>
   <si>
     <t>Jony Rathor</t>
   </si>
   <si>
+    <t>akbk6551+1109@gmail.com</t>
+  </si>
+  <si>
+    <t>9834724767</t>
+  </si>
+  <si>
+    <t>Neeraj Rathor</t>
+  </si>
+  <si>
+    <t>akbk6551+1217@gmail.com</t>
+  </si>
+  <si>
+    <t>9834724790</t>
+  </si>
+  <si>
+    <t>Manjeet Singh</t>
+  </si>
+  <si>
+    <t>akbk6551+1215@gmail.com</t>
+  </si>
+  <si>
+    <t>9834794787</t>
+  </si>
+  <si>
+    <t>Susil Rana</t>
+  </si>
+  <si>
+    <t>akbk6551+1214@gmail.com</t>
+  </si>
+  <si>
+    <t>9834724784</t>
+  </si>
+  <si>
+    <t>Shivam maurya</t>
+  </si>
+  <si>
+    <t>akbk6551+1213@gmail.com</t>
+  </si>
+  <si>
+    <t>9834724797</t>
+  </si>
+  <si>
+    <t>Shyam Sundar</t>
+  </si>
+  <si>
+    <t>akbk6551+1212@gmail.com</t>
+  </si>
+  <si>
+    <t>9834724747</t>
+  </si>
+  <si>
     <t>akbk6551+1119@gmail.com</t>
   </si>
   <si>
-    <t>8000000013</t>
-  </si>
-  <si>
-    <t>Neeraj Rathor</t>
-  </si>
-  <si>
-    <t>akbk6551+1217@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000012</t>
-  </si>
-  <si>
-    <t>Manjeet Singh</t>
-  </si>
-  <si>
-    <t>akbk6551+1215@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000011</t>
-  </si>
-  <si>
-    <t>Susil Rana</t>
-  </si>
-  <si>
-    <t>akbk6551+1214@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000010</t>
-  </si>
-  <si>
-    <t>Shivam maurya</t>
-  </si>
-  <si>
-    <t>akbk6551+1213@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000009</t>
-  </si>
-  <si>
-    <t>Shyam Sundar</t>
-  </si>
-  <si>
-    <t>akbk6551+1212@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000008</t>
-  </si>
-  <si>
-    <t>akbk6551+1109@gmail.com</t>
-  </si>
-  <si>
-    <t>8000000007</t>
+    <t>9834724787</t>
   </si>
   <si>
     <t>Imran Khan</t>
@@ -136,7 +127,7 @@
     <t>commercial</t>
   </si>
   <si>
-    <t>8000000005</t>
+    <t>9863576112</t>
   </si>
   <si>
     <t>Sushil Kumar</t>
@@ -151,7 +142,7 @@
     <t>1345836</t>
   </si>
   <si>
-    <t>8000000003</t>
+    <t>9863574192</t>
   </si>
   <si>
     <t>Sushil Singh</t>
@@ -166,7 +157,7 @@
     <t>1245836</t>
   </si>
   <si>
-    <t>8000000001</t>
+    <t>9863574112</t>
   </si>
 </sst>
 </file>
@@ -543,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
@@ -685,90 +676,76 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
         <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
